--- a/artfynd/A 36640-2023 artfynd.xlsx
+++ b/artfynd/A 36640-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137249860</v>
       </c>
       <c r="B2" t="n">
-        <v>81472</v>
+        <v>81482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137249858</v>
       </c>
       <c r="B3" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137249856</v>
       </c>
       <c r="B4" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137249859</v>
       </c>
       <c r="B5" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36640-2023 artfynd.xlsx
+++ b/artfynd/A 36640-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137249860</v>
       </c>
       <c r="B2" t="n">
-        <v>81482</v>
+        <v>81485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137249858</v>
       </c>
       <c r="B3" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137249856</v>
       </c>
       <c r="B4" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137249859</v>
       </c>
       <c r="B5" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36640-2023 artfynd.xlsx
+++ b/artfynd/A 36640-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137249860</v>
       </c>
       <c r="B2" t="n">
-        <v>81485</v>
+        <v>81490</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137249858</v>
       </c>
       <c r="B3" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137249856</v>
       </c>
       <c r="B4" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137249859</v>
       </c>
       <c r="B5" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36640-2023 artfynd.xlsx
+++ b/artfynd/A 36640-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137249860</v>
       </c>
       <c r="B2" t="n">
-        <v>81490</v>
+        <v>81501</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137249858</v>
       </c>
       <c r="B3" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137249856</v>
       </c>
       <c r="B4" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137249859</v>
       </c>
       <c r="B5" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36640-2023 artfynd.xlsx
+++ b/artfynd/A 36640-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137249860</v>
       </c>
       <c r="B2" t="n">
-        <v>81501</v>
+        <v>81502</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137249858</v>
       </c>
       <c r="B3" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137249856</v>
       </c>
       <c r="B4" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137249859</v>
       </c>
       <c r="B5" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36640-2023 artfynd.xlsx
+++ b/artfynd/A 36640-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137249860</v>
       </c>
       <c r="B2" t="n">
-        <v>81502</v>
+        <v>81504</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137249858</v>
       </c>
       <c r="B3" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137249856</v>
       </c>
       <c r="B4" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137249859</v>
       </c>
       <c r="B5" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36640-2023 artfynd.xlsx
+++ b/artfynd/A 36640-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137249860</v>
       </c>
       <c r="B2" t="n">
-        <v>81504</v>
+        <v>81508</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>137249858</v>
       </c>
       <c r="B3" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>137249856</v>
       </c>
       <c r="B4" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>137249859</v>
       </c>
       <c r="B5" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
